--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.24344733406151</v>
+        <v>4.102060191784995</v>
       </c>
       <c r="D2" t="n">
-        <v>24.99490069704067</v>
+        <v>4.061671363269109</v>
       </c>
       <c r="E2" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F2" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.499854712632169</v>
+        <v>1.543726390802728</v>
       </c>
       <c r="D3" t="n">
-        <v>9.671004249793782</v>
+        <v>1.57153819059149</v>
       </c>
       <c r="E3" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F3" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.55194058849199</v>
+        <v>2.202190345629948</v>
       </c>
       <c r="D4" t="n">
-        <v>13.35383638858927</v>
+        <v>2.169998413145757</v>
       </c>
       <c r="E4" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F4" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.03590411290059</v>
+        <v>4.555834418346346</v>
       </c>
       <c r="D5" t="n">
-        <v>28.27695934085009</v>
+        <v>4.595005892888141</v>
       </c>
       <c r="E5" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F5" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.93734137316321</v>
+        <v>9.089817973139022</v>
       </c>
       <c r="D6" t="n">
-        <v>56.00658268202206</v>
+        <v>9.101069685828584</v>
       </c>
       <c r="E6" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F6" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.41008506236082</v>
+        <v>10.95413882263363</v>
       </c>
       <c r="D7" t="n">
-        <v>66.4987589975475</v>
+        <v>10.80604833710147</v>
       </c>
       <c r="E7" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F7" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.1339784040091</v>
+        <v>5.546771490651479</v>
       </c>
       <c r="D8" t="n">
-        <v>34.19449319381604</v>
+        <v>5.556605143995108</v>
       </c>
       <c r="E8" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F8" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.85311880633294</v>
+        <v>8.263631806029103</v>
       </c>
       <c r="D9" t="n">
-        <v>50.88154676978854</v>
+        <v>8.268251350090637</v>
       </c>
       <c r="E9" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F9" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.84004706242656</v>
+        <v>8.261507647644317</v>
       </c>
       <c r="D10" t="n">
-        <v>50.19003342898358</v>
+        <v>8.155880432209832</v>
       </c>
       <c r="E10" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F10" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.58404875782884</v>
+        <v>6.919907923147187</v>
       </c>
       <c r="D11" t="n">
-        <v>42.72773289531439</v>
+        <v>6.943256595488588</v>
       </c>
       <c r="E11" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F11" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.62523796470709</v>
+        <v>5.951601169264903</v>
       </c>
       <c r="D12" t="n">
-        <v>37.65514831481892</v>
+        <v>6.118961601158075</v>
       </c>
       <c r="E12" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F12" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.54983776683779</v>
+        <v>5.776848637111141</v>
       </c>
       <c r="D13" t="n">
-        <v>37.54279406176865</v>
+        <v>6.100704035037406</v>
       </c>
       <c r="E13" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F13" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.89533845326509</v>
+        <v>7.782992498655577</v>
       </c>
       <c r="D14" t="n">
-        <v>47.77845224978955</v>
+        <v>7.763998490590803</v>
       </c>
       <c r="E14" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F14" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.9358488235972</v>
+        <v>6.327075433834546</v>
       </c>
       <c r="D15" t="n">
-        <v>36.57363648137525</v>
+        <v>5.943215928223479</v>
       </c>
       <c r="E15" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F15" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.82069476394246</v>
+        <v>9.07086289914065</v>
       </c>
       <c r="D16" t="n">
-        <v>55.70921404340837</v>
+        <v>9.052747282053859</v>
       </c>
       <c r="E16" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F16" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.6175105237043</v>
+        <v>6.275345460101948</v>
       </c>
       <c r="D17" t="n">
-        <v>41.06103379768654</v>
+        <v>6.672417992124063</v>
       </c>
       <c r="E17" t="n">
-        <v>15.03067316028026</v>
+        <v>2.442484388545542</v>
       </c>
       <c r="F17" t="n">
-        <v>14.88068556253026</v>
+        <v>2.418111403911167</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
